--- a/knowledge-pack/wps/WPS_Blocking_Template_REPAIRED.xlsx
+++ b/knowledge-pack/wps/WPS_Blocking_Template_REPAIRED.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Macro_Log" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Validation" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="prompts_to_send" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ContinuationTiming" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="Config_Table">Config!$D$1:$I$10</definedName>
@@ -1585,6 +1586,178 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>BlockDurationSec</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>BaseMinWords</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>BaseSafeWords</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>BaseMaxWords</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>LipSyncTargetMin</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>LipSyncTargetMax</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>FaceVisibleFirstSeconds</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>DialogueStartTarget</t>
+        </is>
+      </c>
+      <c r="K1" s="12" t="inlineStr">
+        <is>
+          <t>NoCutawayUntilLipSyncEstablished</t>
+        </is>
+      </c>
+      <c r="L1" s="12" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Malay</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1-2s</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>first 0.2-0.5s</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Soft continuation target only. Keep retained base WPS authority unchanged and do not approve 8-10-word Malay continuation clips.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Google Flow</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Malay</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1-2s</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>first 0.2-0.5s</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Continuation target stays inside retained Malay WPS authority while biasing faster visible lipsync startup.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
